--- a/DataTables/Datas/__tables__.xlsx
+++ b/DataTables/Datas/__tables__.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaboom\Downloads\Lcc-master\Lcc-master\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DABD245-6BAB-42EF-AB65-2FA1A4748A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB348CB2-94B8-4ACC-BC23-089ECD75FDAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="57">
   <si>
     <t>##var</t>
   </si>
@@ -132,33 +132,6 @@
   </si>
   <si>
     <t>popupPanel.xlsx</t>
-  </si>
-  <si>
-    <t>TBSkill</t>
-  </si>
-  <si>
-    <t>Skill</t>
-  </si>
-  <si>
-    <t>skill.xlsx</t>
-  </si>
-  <si>
-    <t>TBBuff</t>
-  </si>
-  <si>
-    <t>Buff</t>
-  </si>
-  <si>
-    <t>buff.xlsx</t>
-  </si>
-  <si>
-    <t>TBSubobject</t>
-  </si>
-  <si>
-    <t>Subobject</t>
-  </si>
-  <si>
-    <t>subobject.xlsx</t>
   </si>
   <si>
     <t>TBLanguage</t>
@@ -587,7 +560,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -772,101 +745,59 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B10" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" t="s">
-        <v>46</v>
+      <c r="B10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
-      <c r="E10" t="s">
-        <v>47</v>
+      <c r="E10" s="2" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B11" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="B12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="B13" t="s">
         <v>51</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="s">
         <v>53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B14" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>55</v>
-      </c>
-      <c r="D14" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" t="s">
-        <v>58</v>
-      </c>
-      <c r="D15" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="B16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" t="s">
-        <v>61</v>
-      </c>
-      <c r="D16" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>62</v>
       </c>
     </row>
   </sheetData>
